--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/3041-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/3041-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{63EABDAA-F3EF-4FD6-B5BB-39170171EF7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{200CD6C1-35A4-4F6E-9103-DE5E4C35F054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{8D9A5520-7858-40C2-89A5-A2528746DA63}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{F63F594E-C232-44AE-9514-820A9F9DA9FA}"/>
   </bookViews>
   <sheets>
     <sheet name="3041-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1487,30 +1487,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32576BAC-B7CD-40B2-A784-AAB276FEAA25}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{559FBCA2-4E5C-4588-88EB-5EED22FA1E29}">
   <dimension ref="A1:X48"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1544,7 +1544,7 @@
       <c r="W1" s="29"/>
       <c r="X1" s="21"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
@@ -1580,7 +1580,7 @@
       <c r="W2" s="31"/>
       <c r="X2" s="32"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="X3" s="35"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="24"/>
       <c r="B4" s="25"/>
       <c r="C4" s="7"/>
@@ -1700,7 +1700,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="36">
         <v>2025</v>
       </c>
@@ -1772,7 +1772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1846,7 +1846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="38">
         <v>2024</v>
       </c>
@@ -1918,7 +1918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>29</v>
       </c>
@@ -1992,7 +1992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2066,7 +2066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>29</v>
       </c>
@@ -2140,7 +2140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
@@ -2214,7 +2214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="36">
         <v>2023</v>
       </c>
@@ -2286,7 +2286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>29</v>
       </c>
@@ -2360,7 +2360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>29</v>
       </c>
@@ -2434,7 +2434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>29</v>
       </c>
@@ -2508,7 +2508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>29</v>
       </c>
@@ -2582,7 +2582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="38">
         <v>2022</v>
       </c>
@@ -2654,7 +2654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
         <v>29</v>
       </c>
@@ -2728,7 +2728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="16" t="s">
         <v>29</v>
       </c>
@@ -2802,7 +2802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="36">
         <v>2021</v>
       </c>
@@ -2874,7 +2874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="38">
         <v>2020</v>
       </c>
@@ -2946,7 +2946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="36">
         <v>2019</v>
       </c>
@@ -3018,7 +3018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="38">
         <v>2018</v>
       </c>
@@ -3090,7 +3090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="36">
         <v>2017</v>
       </c>
@@ -3162,7 +3162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="38">
         <v>2016</v>
       </c>
@@ -3234,7 +3234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="36">
         <v>2015</v>
       </c>
@@ -3306,7 +3306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="38">
         <v>2014</v>
       </c>
@@ -3378,7 +3378,7 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="36">
         <v>2013</v>
       </c>
@@ -3450,7 +3450,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="38">
         <v>2012</v>
       </c>
@@ -3522,7 +3522,7 @@
         <v>7.07</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="36">
         <v>2011</v>
       </c>
@@ -3594,7 +3594,7 @@
         <v>6.18</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="38">
         <v>2010</v>
       </c>
@@ -3666,7 +3666,7 @@
         <v>9.99</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="36">
         <v>2009</v>
       </c>
@@ -3738,7 +3738,7 @@
         <v>4.78</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="38">
         <v>2008</v>
       </c>
@@ -3810,7 +3810,7 @@
         <v>2.29</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="36">
         <v>2007</v>
       </c>
@@ -3882,7 +3882,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="38">
         <v>2006</v>
       </c>
@@ -3954,7 +3954,7 @@
         <v>3.03</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="36">
         <v>2005</v>
       </c>
@@ -4026,7 +4026,7 @@
         <v>2.92</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="38">
         <v>2004</v>
       </c>
@@ -4098,7 +4098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="36">
         <v>2003</v>
       </c>
@@ -4170,7 +4170,7 @@
         <v>3.52</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="38">
         <v>2002</v>
       </c>
@@ -4242,7 +4242,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="36">
         <v>2001</v>
       </c>
@@ -4314,7 +4314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="38">
         <v>2000</v>
       </c>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="36">
         <v>1999</v>
       </c>
@@ -4458,7 +4458,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="38">
         <v>1998</v>
       </c>
@@ -4530,7 +4530,7 @@
         <v>1.29</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="36">
         <v>1997</v>
       </c>
@@ -4602,7 +4602,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="38">
         <v>1996</v>
       </c>
@@ -4674,7 +4674,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="36">
         <v>1995</v>
       </c>
@@ -4746,7 +4746,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="38">
         <v>1994</v>
       </c>
@@ -4818,7 +4818,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="36" t="s">
         <v>49</v>
       </c>
